--- a/artfynd/A 29917-2024 artfynd.xlsx
+++ b/artfynd/A 29917-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175265</v>
+        <v>120175409</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582377</v>
+        <v>582403</v>
       </c>
       <c r="R2" t="n">
-        <v>7025961</v>
+        <v>7025936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120175409</v>
+        <v>120175265</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582403</v>
+        <v>582377</v>
       </c>
       <c r="R3" t="n">
-        <v>7025936</v>
+        <v>7025961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29917-2024 artfynd.xlsx
+++ b/artfynd/A 29917-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175409</v>
+        <v>120175265</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582403</v>
+        <v>582377</v>
       </c>
       <c r="R2" t="n">
-        <v>7025936</v>
+        <v>7025961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120175265</v>
+        <v>120175409</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582377</v>
+        <v>582403</v>
       </c>
       <c r="R3" t="n">
-        <v>7025961</v>
+        <v>7025936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
